--- a/Excel9to10/data.xlsx
+++ b/Excel9to10/data.xlsx
@@ -1,31 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AllData\Excel9to10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45DFA506-69DB-437E-94E0-DFB2A8C72CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BFA526-4588-4688-A0DF-458ED7279DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A926CD0A-2EC9-4639-B6BF-DF3120631196}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A926CD0A-2EC9-4639-B6BF-DF3120631196}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet4" sheetId="4" r:id="rId1"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
-    <sheet name="RegionVsSales" sheetId="3" r:id="rId4"/>
-    <sheet name="UnitSoldBySalesPerson" sheetId="2" r:id="rId5"/>
+    <sheet name="Dashboard" sheetId="6" r:id="rId1"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="7" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="RegionVsSales" sheetId="3" r:id="rId6"/>
+    <sheet name="UnitSoldBySalesPerson" sheetId="2" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="NativeTimeline_Date">#N/A</definedName>
+    <definedName name="Slicer_Product">#N/A</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId6"/>
-    <pivotCache cacheId="13" r:id="rId7"/>
-    <pivotCache cacheId="21" r:id="rId8"/>
+    <pivotCache cacheId="3" r:id="rId8"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
+    <pivotCache cacheId="2" r:id="rId10"/>
+    <pivotCache cacheId="7" r:id="rId11"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId12"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}">
+      <x15:timelineCacheRefs>
+        <x15:timelineCacheRef r:id="rId13"/>
+      </x15:timelineCacheRefs>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -46,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="29">
   <si>
     <t>Date</t>
   </si>
@@ -128,12 +148,18 @@
   <si>
     <t>Sum of Total_Sale</t>
   </si>
+  <si>
+    <t>DASHBOARD</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,16 +167,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="28"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Arial Rounded MT Bold"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -173,11 +211,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -189,6 +238,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -215,6 +269,1126 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[data.xlsx]Sheet4!PivotTable4</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="brightRoom" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="flat">
+            <a:bevelT w="50800" h="101600" prst="angle"/>
+            <a:contourClr>
+              <a:srgbClr val="000000"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="brightRoom" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="flat">
+            <a:bevelT w="50800" h="101600" prst="angle"/>
+            <a:contourClr>
+              <a:srgbClr val="000000"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="brightRoom" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="flat">
+            <a:bevelT w="50800" h="101600" prst="angle"/>
+            <a:contourClr>
+              <a:srgbClr val="000000"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="brightRoom" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="flat">
+            <a:bevelT w="50800" h="101600" prst="angle"/>
+            <a:contourClr>
+              <a:srgbClr val="000000"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="brightRoom" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="flat">
+            <a:bevelT w="50800" h="101600" prst="angle"/>
+            <a:contourClr>
+              <a:srgbClr val="000000"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="brightRoom" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="flat">
+            <a:bevelT w="50800" h="101600" prst="angle"/>
+            <a:contourClr>
+              <a:srgbClr val="000000"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="brightRoom" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="flat">
+            <a:bevelT w="50800" h="101600" prst="angle"/>
+            <a:contourClr>
+              <a:srgbClr val="000000"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="brightRoom" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="flat">
+            <a:bevelT w="50800" h="101600" prst="angle"/>
+            <a:contourClr>
+              <a:srgbClr val="000000"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="brightRoom" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="flat">
+            <a:bevelT w="50800" h="101600" prst="angle"/>
+            <a:contourClr>
+              <a:srgbClr val="000000"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="brightRoom" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="flat">
+            <a:bevelT w="50800" h="101600" prst="angle"/>
+            <a:contourClr>
+              <a:srgbClr val="000000"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="brightRoom" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="flat">
+            <a:bevelT w="50800" h="101600" prst="angle"/>
+            <a:contourClr>
+              <a:srgbClr val="000000"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet4!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="brightRoom" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="flat">
+                <a:bevelT w="50800" h="101600" prst="angle"/>
+                <a:contourClr>
+                  <a:srgbClr val="000000"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-A88F-4607-ADC0-DCB1911AFA6B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="brightRoom" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="flat">
+                <a:bevelT w="50800" h="101600" prst="angle"/>
+                <a:contourClr>
+                  <a:srgbClr val="000000"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-A88F-4607-ADC0-DCB1911AFA6B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="brightRoom" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="flat">
+                <a:bevelT w="50800" h="101600" prst="angle"/>
+                <a:contourClr>
+                  <a:srgbClr val="000000"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-A88F-4607-ADC0-DCB1911AFA6B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="brightRoom" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="flat">
+                <a:bevelT w="50800" h="101600" prst="angle"/>
+                <a:contourClr>
+                  <a:srgbClr val="000000"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-A88F-4607-ADC0-DCB1911AFA6B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet4!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet4!$B$4:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>511</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>402</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>382</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>340</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-A88F-4607-ADC0-DCB1911AFA6B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="50"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[data.xlsx]Sheet4!PivotTable4</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="brightRoom" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="flat">
+            <a:bevelT w="50800" h="101600" prst="angle"/>
+            <a:contourClr>
+              <a:srgbClr val="000000"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet4!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="brightRoom" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="flat">
+                <a:bevelT w="50800" h="101600" prst="angle"/>
+                <a:contourClr>
+                  <a:srgbClr val="000000"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="brightRoom" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="flat">
+                <a:bevelT w="50800" h="101600" prst="angle"/>
+                <a:contourClr>
+                  <a:srgbClr val="000000"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="brightRoom" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="flat">
+                <a:bevelT w="50800" h="101600" prst="angle"/>
+                <a:contourClr>
+                  <a:srgbClr val="000000"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="brightRoom" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="flat">
+                <a:bevelT w="50800" h="101600" prst="angle"/>
+                <a:contourClr>
+                  <a:srgbClr val="000000"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet4!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet4!$B$4:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>511</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>402</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>382</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>340</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B712-4CEE-BA5F-D41B00095EAB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="50"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1007,7 +2181,410 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[data.xlsx]RegionVsSales!PivotTable2</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>RegionVsSales!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>RegionVsSales!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>RegionVsSales!$B$4:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>69450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>33301</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>126790</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>37455</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C249-4125-B2E4-BEA5EC0CD1E6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1247135615"/>
+        <c:axId val="1247136031"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1247135615"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1247136031"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1247136031"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1247135615"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1422,7 +2999,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1490,19 +3067,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1746,6 +3311,7 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="189702575"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -1804,6 +3370,7 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="189702095"/>
+        <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
@@ -1954,13 +3521,133 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="17">
   <a:schemeClr val="accent4"/>
 </cs:colorStyle>
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="258">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1971,7 +3658,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -1983,17 +3670,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
@@ -2017,19 +3693,16 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
     <cs:lnRef idx="0"/>
@@ -2061,29 +3734,54 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:scene3d>
+        <a:camera prst="orthographicFront"/>
+        <a:lightRig rig="brightRoom" dir="t"/>
+      </a:scene3d>
+      <a:sp3d prstMaterial="flat">
+        <a:bevelT w="50800" h="101600" prst="angle"/>
+        <a:contourClr>
+          <a:srgbClr val="000000"/>
+        </a:contourClr>
+      </a:sp3d>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -2098,10 +3796,8 @@
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
@@ -2109,19 +3805,22 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -2164,22 +3863,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -2284,8 +3984,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2380,7 +4080,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1400" b="1" i="0" kern="1200" cap="all" spc="50" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -2396,7 +4096,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
+        <a:prstDash val="sysDash"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -2417,19 +4117,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -2463,7 +4164,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="258">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2474,7 +4175,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -2486,17 +4187,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
@@ -2520,19 +4210,16 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
     <cs:lnRef idx="0"/>
@@ -2564,6 +4251,537 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:scene3d>
+        <a:camera prst="orthographicFront"/>
+        <a:lightRig rig="brightRoom" dir="t"/>
+      </a:scene3d>
+      <a:sp3d prstMaterial="flat">
+        <a:bevelT w="50800" h="101600" prst="angle"/>
+        <a:contourClr>
+          <a:srgbClr val="000000"/>
+        </a:contourClr>
+      </a:sp3d>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" i="0" kern="1200" cap="all" spc="50" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
     <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
@@ -2965,7 +5183,1013 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="259">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3486,6 +6710,227 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>256190</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>13138</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>177363</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>32845</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle: Rounded Corners 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1401688-6E52-4F2E-9DF1-D70D3F9286C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1478018" y="775138"/>
+          <a:ext cx="1753914" cy="972207"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="2000"/>
+            <a:t>25,45,558</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1050"/>
+            <a:t>Total</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1050" baseline="0"/>
+            <a:t> Sales</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="2000"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>455887</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>15766</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>377060</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>35473</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Rectangle: Rounded Corners 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC03387F-7A68-4A8E-A734-1F988CAA1D88}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9008680" y="777766"/>
+          <a:ext cx="1753914" cy="972207"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>275899</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>26277</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>348158</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>13139</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A0808F5-497F-4E26-BDA4-A4A85DA20C5D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4E33339-6C5B-41A0-AAF1-1E8AB5A17DAF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3526,7 +6971,208 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>314324</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>171451</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Date">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{722626DD-3203-4664-87E2-3140E5492769}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
+              <tsle:timeslicer xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" name="Date"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2314574" y="390525"/>
+              <a:ext cx="3667126" cy="1114426"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>Timeline: Works in Excel 2013 or higher. Do not move or resize.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>933450</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Product">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DB494A4-B916-4DF9-90A8-103263B4FBB2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Product"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2686050" y="714375"/>
+              <a:ext cx="1828800" cy="1724025"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC92CEF2-27F2-4E0D-8C01-62E95F786A47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3651,7 +7297,7 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
+      <x14:pivotCacheDefinition pivotCacheId="977216635"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -3806,6 +7452,111 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="RWR2" refreshedDate="46140.398388888891" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="59" xr:uid="{0E1ACCBF-C700-4218-9B49-54E5C61DAFE6}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:H60" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="8">
+    <cacheField name="Date" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-01-01T00:00:00" maxDate="2026-03-01T00:00:00" count="59">
+        <d v="2024-01-01T00:00:00"/>
+        <d v="2024-01-02T00:00:00"/>
+        <d v="2024-01-03T00:00:00"/>
+        <d v="2024-01-04T00:00:00"/>
+        <d v="2024-01-05T00:00:00"/>
+        <d v="2024-01-06T00:00:00"/>
+        <d v="2024-01-07T00:00:00"/>
+        <d v="2024-01-08T00:00:00"/>
+        <d v="2024-01-09T00:00:00"/>
+        <d v="2024-01-10T00:00:00"/>
+        <d v="2024-01-11T00:00:00"/>
+        <d v="2024-01-12T00:00:00"/>
+        <d v="2024-01-13T00:00:00"/>
+        <d v="2024-01-14T00:00:00"/>
+        <d v="2024-01-15T00:00:00"/>
+        <d v="2024-01-16T00:00:00"/>
+        <d v="2024-01-17T00:00:00"/>
+        <d v="2024-01-18T00:00:00"/>
+        <d v="2024-01-19T00:00:00"/>
+        <d v="2024-01-20T00:00:00"/>
+        <d v="2024-01-21T00:00:00"/>
+        <d v="2024-01-22T00:00:00"/>
+        <d v="2024-01-23T00:00:00"/>
+        <d v="2024-01-24T00:00:00"/>
+        <d v="2024-01-25T00:00:00"/>
+        <d v="2024-01-26T00:00:00"/>
+        <d v="2024-01-27T00:00:00"/>
+        <d v="2024-01-28T00:00:00"/>
+        <d v="2024-01-29T00:00:00"/>
+        <d v="2024-01-30T00:00:00"/>
+        <d v="2024-01-31T00:00:00"/>
+        <d v="2024-02-01T00:00:00"/>
+        <d v="2024-02-02T00:00:00"/>
+        <d v="2024-02-03T00:00:00"/>
+        <d v="2024-02-04T00:00:00"/>
+        <d v="2024-02-05T00:00:00"/>
+        <d v="2024-02-06T00:00:00"/>
+        <d v="2024-02-07T00:00:00"/>
+        <d v="2024-02-08T00:00:00"/>
+        <d v="2024-02-09T00:00:00"/>
+        <d v="2024-02-10T00:00:00"/>
+        <d v="2024-02-11T00:00:00"/>
+        <d v="2025-02-12T00:00:00"/>
+        <d v="2025-02-13T00:00:00"/>
+        <d v="2025-02-14T00:00:00"/>
+        <d v="2025-02-15T00:00:00"/>
+        <d v="2025-02-16T00:00:00"/>
+        <d v="2025-02-17T00:00:00"/>
+        <d v="2025-02-18T00:00:00"/>
+        <d v="2025-02-19T00:00:00"/>
+        <d v="2025-02-20T00:00:00"/>
+        <d v="2025-02-21T00:00:00"/>
+        <d v="2025-02-22T00:00:00"/>
+        <d v="2026-02-23T00:00:00"/>
+        <d v="2026-02-24T00:00:00"/>
+        <d v="2026-02-25T00:00:00"/>
+        <d v="2026-02-26T00:00:00"/>
+        <d v="2026-02-27T00:00:00"/>
+        <d v="2026-02-28T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Region" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Product" numFmtId="0">
+      <sharedItems count="5">
+        <s v="Tablet"/>
+        <s v="Headphones"/>
+        <s v="Camera"/>
+        <s v="Mobile"/>
+        <s v="Laptop"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Salesperson" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Units_Sold" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="7" maxValue="50"/>
+    </cacheField>
+    <cacheField name="Unit_Price" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="510" maxValue="1900"/>
+    </cacheField>
+    <cacheField name="Total_Sale" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="417" maxValue="95000"/>
+    </cacheField>
+    <cacheField name="Year" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2024" maxValue="2026"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition pivotCacheId="691698920"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="59">
   <r>
@@ -5414,8 +9165,661 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="59">
+  <r>
+    <x v="0"/>
+    <s v="South"/>
+    <x v="0"/>
+    <s v="Lina"/>
+    <n v="37"/>
+    <n v="1747"/>
+    <n v="64639"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="North"/>
+    <x v="1"/>
+    <s v="Riya"/>
+    <n v="12"/>
+    <n v="514"/>
+    <n v="6168"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="West"/>
+    <x v="2"/>
+    <s v="Sara"/>
+    <n v="41"/>
+    <n v="1444"/>
+    <n v="59204"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="East"/>
+    <x v="3"/>
+    <s v="Amit"/>
+    <n v="8"/>
+    <n v="1013"/>
+    <n v="8104"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="North"/>
+    <x v="4"/>
+    <s v="David"/>
+    <n v="47"/>
+    <n v="1512"/>
+    <n v="71064"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="South"/>
+    <x v="2"/>
+    <s v="John"/>
+    <n v="14"/>
+    <n v="1753"/>
+    <n v="24542"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="East"/>
+    <x v="3"/>
+    <s v="Lina"/>
+    <n v="50"/>
+    <n v="1388"/>
+    <n v="69400"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="South"/>
+    <x v="0"/>
+    <s v="Sara"/>
+    <n v="39"/>
+    <n v="1004"/>
+    <n v="39156"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="East"/>
+    <x v="2"/>
+    <s v="Amit"/>
+    <n v="22"/>
+    <n v="1368"/>
+    <n v="30096"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="West"/>
+    <x v="4"/>
+    <s v="Riya"/>
+    <n v="17"/>
+    <n v="1650"/>
+    <n v="28050"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <s v="North"/>
+    <x v="1"/>
+    <s v="David"/>
+    <n v="21"/>
+    <n v="584"/>
+    <n v="12264"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <s v="South"/>
+    <x v="2"/>
+    <s v="Lina"/>
+    <n v="18"/>
+    <n v="1872"/>
+    <n v="33696"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <s v="East"/>
+    <x v="3"/>
+    <s v="John"/>
+    <n v="44"/>
+    <n v="1305"/>
+    <n v="57420"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <s v="West"/>
+    <x v="4"/>
+    <s v="Sara"/>
+    <n v="10"/>
+    <n v="1788"/>
+    <n v="17880"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <s v="South"/>
+    <x v="0"/>
+    <s v="Amit"/>
+    <n v="13"/>
+    <n v="999"/>
+    <n v="12987"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <s v="North"/>
+    <x v="2"/>
+    <s v="David"/>
+    <n v="27"/>
+    <n v="1801"/>
+    <n v="48627"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <s v="East"/>
+    <x v="3"/>
+    <s v="Lina"/>
+    <n v="48"/>
+    <n v="1104"/>
+    <n v="52992"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <s v="West"/>
+    <x v="1"/>
+    <s v="John"/>
+    <n v="25"/>
+    <n v="693"/>
+    <n v="17325"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <s v="South"/>
+    <x v="0"/>
+    <s v="Riya"/>
+    <n v="9"/>
+    <n v="1112"/>
+    <n v="10008"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="North"/>
+    <x v="2"/>
+    <s v="Sara"/>
+    <n v="46"/>
+    <n v="1609"/>
+    <n v="74014"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <s v="East"/>
+    <x v="3"/>
+    <s v="Amit"/>
+    <n v="31"/>
+    <n v="1520"/>
+    <n v="47120"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <s v="West"/>
+    <x v="4"/>
+    <s v="David"/>
+    <n v="20"/>
+    <n v="1875"/>
+    <n v="37500"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <s v="South"/>
+    <x v="1"/>
+    <s v="Lina"/>
+    <n v="11"/>
+    <n v="553"/>
+    <n v="6083"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <s v="East"/>
+    <x v="2"/>
+    <s v="Riya"/>
+    <n v="34"/>
+    <n v="1399"/>
+    <n v="47566"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <s v="North"/>
+    <x v="3"/>
+    <s v="John"/>
+    <n v="28"/>
+    <n v="1066"/>
+    <n v="29848"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <s v="West"/>
+    <x v="0"/>
+    <s v="Sara"/>
+    <n v="15"/>
+    <n v="945"/>
+    <n v="14175"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="26"/>
+    <s v="South"/>
+    <x v="2"/>
+    <s v="Amit"/>
+    <n v="41"/>
+    <n v="1780"/>
+    <n v="72980"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <s v="North"/>
+    <x v="4"/>
+    <s v="David"/>
+    <n v="19"/>
+    <n v="1899"/>
+    <n v="36081"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <s v="East"/>
+    <x v="1"/>
+    <s v="Lina"/>
+    <n v="23"/>
+    <n v="669"/>
+    <n v="15387"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="29"/>
+    <s v="West"/>
+    <x v="3"/>
+    <s v="John"/>
+    <n v="36"/>
+    <n v="1177"/>
+    <n v="42372"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="30"/>
+    <s v="South"/>
+    <x v="2"/>
+    <s v="Sara"/>
+    <n v="29"/>
+    <n v="1650"/>
+    <n v="47850"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="31"/>
+    <s v="North"/>
+    <x v="0"/>
+    <s v="Amit"/>
+    <n v="17"/>
+    <n v="899"/>
+    <n v="15283"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="32"/>
+    <s v="East"/>
+    <x v="3"/>
+    <s v="Lina"/>
+    <n v="45"/>
+    <n v="1240"/>
+    <n v="55800"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="33"/>
+    <s v="West"/>
+    <x v="1"/>
+    <s v="David"/>
+    <n v="30"/>
+    <n v="721"/>
+    <n v="21630"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <s v="North"/>
+    <x v="4"/>
+    <s v="John"/>
+    <n v="50"/>
+    <n v="1900"/>
+    <n v="95000"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="35"/>
+    <s v="South"/>
+    <x v="2"/>
+    <s v="Riya"/>
+    <n v="32"/>
+    <n v="1550"/>
+    <n v="49600"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="36"/>
+    <s v="East"/>
+    <x v="0"/>
+    <s v="Lina"/>
+    <n v="44"/>
+    <n v="1020"/>
+    <n v="44880"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="37"/>
+    <s v="West"/>
+    <x v="3"/>
+    <s v="Sara"/>
+    <n v="38"/>
+    <n v="1211"/>
+    <n v="46018"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="38"/>
+    <s v="North"/>
+    <x v="2"/>
+    <s v="Amit"/>
+    <n v="14"/>
+    <n v="1488"/>
+    <n v="20832"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="39"/>
+    <s v="East"/>
+    <x v="4"/>
+    <s v="John"/>
+    <n v="22"/>
+    <n v="1750"/>
+    <n v="38500"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="40"/>
+    <s v="South"/>
+    <x v="1"/>
+    <s v="David"/>
+    <n v="7"/>
+    <n v="510"/>
+    <n v="3570"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="41"/>
+    <s v="West"/>
+    <x v="3"/>
+    <s v="Riya"/>
+    <n v="28"/>
+    <n v="1330"/>
+    <n v="37240"/>
+    <n v="2024"/>
+  </r>
+  <r>
+    <x v="42"/>
+    <s v="North"/>
+    <x v="2"/>
+    <s v="Sara"/>
+    <n v="40"/>
+    <n v="1800"/>
+    <n v="72000"/>
+    <n v="2025"/>
+  </r>
+  <r>
+    <x v="43"/>
+    <s v="East"/>
+    <x v="0"/>
+    <s v="Amit"/>
+    <n v="26"/>
+    <n v="945"/>
+    <n v="24570"/>
+    <n v="2025"/>
+  </r>
+  <r>
+    <x v="44"/>
+    <s v="South"/>
+    <x v="3"/>
+    <s v="John"/>
+    <n v="34"/>
+    <n v="1122"/>
+    <n v="38148"/>
+    <n v="2025"/>
+  </r>
+  <r>
+    <x v="45"/>
+    <s v="West"/>
+    <x v="2"/>
+    <s v="Lina"/>
+    <n v="16"/>
+    <n v="1700"/>
+    <n v="27200"/>
+    <n v="2025"/>
+  </r>
+  <r>
+    <x v="46"/>
+    <s v="North"/>
+    <x v="4"/>
+    <s v="David"/>
+    <n v="21"/>
+    <n v="1555"/>
+    <n v="32655"/>
+    <n v="2025"/>
+  </r>
+  <r>
+    <x v="47"/>
+    <s v="East"/>
+    <x v="1"/>
+    <s v="Riya"/>
+    <n v="13"/>
+    <n v="602"/>
+    <n v="7826"/>
+    <n v="2025"/>
+  </r>
+  <r>
+    <x v="48"/>
+    <s v="South"/>
+    <x v="2"/>
+    <s v="Sara"/>
+    <n v="49"/>
+    <n v="1660"/>
+    <n v="81340"/>
+    <n v="2025"/>
+  </r>
+  <r>
+    <x v="49"/>
+    <s v="West"/>
+    <x v="3"/>
+    <s v="Lina"/>
+    <n v="30"/>
+    <n v="1099"/>
+    <n v="32970"/>
+    <n v="2025"/>
+  </r>
+  <r>
+    <x v="50"/>
+    <s v="North"/>
+    <x v="0"/>
+    <s v="John"/>
+    <n v="18"/>
+    <n v="1001"/>
+    <n v="18018"/>
+    <n v="2025"/>
+  </r>
+  <r>
+    <x v="51"/>
+    <s v="East"/>
+    <x v="2"/>
+    <s v="David"/>
+    <n v="37"/>
+    <n v="1577"/>
+    <n v="58349"/>
+    <n v="2025"/>
+  </r>
+  <r>
+    <x v="52"/>
+    <s v="South"/>
+    <x v="4"/>
+    <s v="Amit"/>
+    <n v="29"/>
+    <n v="1820"/>
+    <n v="52780"/>
+    <n v="2025"/>
+  </r>
+  <r>
+    <x v="53"/>
+    <s v="West"/>
+    <x v="1"/>
+    <s v="Riya"/>
+    <n v="10"/>
+    <n v="588"/>
+    <n v="5880"/>
+    <n v="2026"/>
+  </r>
+  <r>
+    <x v="54"/>
+    <s v="East"/>
+    <x v="3"/>
+    <s v="Lina"/>
+    <n v="33"/>
+    <n v="1288"/>
+    <n v="42504"/>
+    <n v="2026"/>
+  </r>
+  <r>
+    <x v="55"/>
+    <s v="North"/>
+    <x v="2"/>
+    <s v="John"/>
+    <n v="42"/>
+    <n v="1677"/>
+    <n v="70434"/>
+    <n v="2026"/>
+  </r>
+  <r>
+    <x v="56"/>
+    <s v="South"/>
+    <x v="4"/>
+    <s v="Sara"/>
+    <n v="20"/>
+    <n v="1900"/>
+    <n v="38000"/>
+    <n v="2026"/>
+  </r>
+  <r>
+    <x v="57"/>
+    <s v="West"/>
+    <x v="0"/>
+    <s v="David"/>
+    <n v="24"/>
+    <n v="970"/>
+    <n v="23280"/>
+    <n v="2026"/>
+  </r>
+  <r>
+    <x v="58"/>
+    <s v="East"/>
+    <x v="3"/>
+    <s v="Amit"/>
+    <n v="31"/>
+    <n v="1344"/>
+    <n v="417"/>
+    <n v="2026"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{66A2C1A1-7F31-44DA-B8F0-0D2ACE186F3D}" name="PivotTable4" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5B89485D-2C42-4EFC-9353-1E54A90710C9}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C16:D21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total_Sale" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleMedium17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{66A2C1A1-7F31-44DA-B8F0-0D2ACE186F3D}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField numFmtId="14" showAll="0"/>
@@ -5460,6 +9864,74 @@
   <dataFields count="1">
     <dataField name="Sum of Units_Sold" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -5472,8 +9944,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4124D157-4772-4675-AA49-A9F6374727F5}" name="PivotTable6" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4124D157-4772-4675-AA49-A9F6374727F5}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:F11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField axis="axisRow" numFmtId="14" showAll="0">
@@ -5677,8 +10149,226 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{29EE6F18-E2A5-43A0-9ED9-23EF41357E3E}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{53182268-4254-4A6B-9738-BC152710E461}" name="PivotTable4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField numFmtId="14" showAll="0">
+      <items count="60">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total_Sale" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="dateBetween" evalOrder="-1" id="8" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="45292"/>
+            <customFilter operator="lessThanOrEqual" val="45657"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{08A1E8C6-78E1-44D3-8D08-07D47D5A383A}" name="salesperson" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B20:C27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Units_Sold" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{29EE6F18-E2A5-43A0-9ED9-23EF41357E3E}" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField numFmtId="14" showAll="0"/>
@@ -5691,7 +10381,16 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -5723,6 +10422,17 @@
   <dataFields count="1">
     <dataField name="Sum of Total_Sale" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -5735,8 +10445,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2FFF9810-E9A4-4040-A1C5-A9D3F16A9D39}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2FFF9810-E9A4-4040-A1C5-A9D3F16A9D39}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField numFmtId="14" showAll="0"/>
@@ -5838,10 +10548,36 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Product" xr10:uid="{8BB1449F-15E7-4132-9E13-99DEEE47185B}" sourceName="Product">
+  <pivotTables>
+    <pivotTable tabId="3" name="PivotTable2"/>
+    <pivotTable tabId="3" name="salesperson"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="977216635">
+      <items count="5">
+        <i x="2"/>
+        <i x="1"/>
+        <i x="4"/>
+        <i x="3"/>
+        <i x="0" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Product" xr10:uid="{6CD2EF75-F97A-4777-88C5-41B76CB2D748}" cache="Slicer_Product" caption="Product" style="SlicerStyleDark4" rowHeight="241300"/>
+</slicers>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5879,7 +10615,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5985,7 +10721,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6127,13 +10863,742 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
+<file path=xl/timelineCaches/timelineCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<timelineCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="xr10" name="NativeTimeline_Date" xr10:uid="{DCE7A299-B0FD-4CAA-866C-2AB6DBA8267E}" sourceName="Date">
+  <pivotTables>
+    <pivotTable tabId="7" name="PivotTable4"/>
+  </pivotTables>
+  <state minimalRefreshVersion="6" lastRefreshVersion="6" pivotCacheId="691698920" filterType="dateBetween">
+    <selection startDate="2024-01-01T00:00:00" endDate="2024-12-31T00:00:00"/>
+    <bounds startDate="2024-01-01T00:00:00" endDate="2027-01-01T00:00:00"/>
+  </state>
+</timelineCacheDefinition>
+</file>
+
+<file path=xl/timelines/timeline1.xml><?xml version="1.0" encoding="utf-8"?>
+<timelines xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <timeline name="Date" xr10:uid="{CECDCC39-149C-4D0A-A107-E32FE68744B7}" cache="NativeTimeline_Date" caption="Date" level="0" selectionLevel="0" scrollPosition="2024-01-01T00:00:00" style="TimeSlicerStyleLight6"/>
+</timelines>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F26293AB-70D3-4CB9-AB2E-31682B3EC923}">
+  <dimension ref="A1:U29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="9"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="9"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="8">
+        <v>600931</v>
+      </c>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="8">
+        <v>602288</v>
+      </c>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="8">
+        <v>575379</v>
+      </c>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="8">
+        <v>410724</v>
+      </c>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="9"/>
+      <c r="U20" s="9"/>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="8">
+        <v>2189322</v>
+      </c>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
+      <c r="S22" s="9"/>
+      <c r="T22" s="9"/>
+      <c r="U22" s="9"/>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="9"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9"/>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+      <c r="S28" s="9"/>
+      <c r="T28" s="9"/>
+      <c r="U28" s="9"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G1:N3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A205B85-463F-42BC-9972-787921B426E8}">
   <dimension ref="A3:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6192,10 +11657,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E0BE562-3F96-4B95-BFF5-8EF1CFC67C5A}">
   <dimension ref="A3:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6374,18 +11840,96 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C622BD5F-E213-43C5-BC60-ECA7F80C92EF}">
+  <dimension ref="A3:B9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="8">
+        <v>509007</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="8">
+        <v>82427</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="8">
+        <v>324075</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="8">
+        <v>446314</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="8">
+        <v>201128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="8">
+        <v>1562951</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{7E03D99C-DC04-49d9-9315-930204A7B6E9}">
+      <x15:timelineRefs>
+        <x15:timelineRef r:id="rId3"/>
+      </x15:timelineRefs>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C103BCB5-16C7-473B-9092-67518EE41015}">
   <dimension ref="A1:K60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -6405,6 +11949,9 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -6429,6 +11976,10 @@
       <c r="G2" s="1">
         <v>64639</v>
       </c>
+      <c r="H2">
+        <f>YEAR(A2)</f>
+        <v>2024</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
@@ -6452,6 +12003,10 @@
       <c r="G3" s="1">
         <v>6168</v>
       </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H60" si="0">YEAR(A3)</f>
+        <v>2024</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -6475,6 +12030,10 @@
       <c r="G4" s="1">
         <v>59204</v>
       </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -6498,6 +12057,10 @@
       <c r="G5" s="1">
         <v>8104</v>
       </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -6521,6 +12084,10 @@
       <c r="G6" s="1">
         <v>71064</v>
       </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -6544,6 +12111,10 @@
       <c r="G7" s="1">
         <v>24542</v>
       </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
@@ -6566,6 +12137,10 @@
       </c>
       <c r="G8" s="1">
         <v>69400</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>2024</v>
       </c>
       <c r="J8" s="4"/>
     </row>
@@ -6591,6 +12166,10 @@
       <c r="G9" s="1">
         <v>39156</v>
       </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -6613,6 +12192,10 @@
       </c>
       <c r="G10" s="1">
         <v>30096</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>2024</v>
       </c>
       <c r="J10" s="3"/>
     </row>
@@ -6638,6 +12221,10 @@
       <c r="G11" s="1">
         <v>28050</v>
       </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -6662,6 +12249,10 @@
       <c r="G12" s="1">
         <v>12264</v>
       </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -6685,6 +12276,10 @@
       <c r="G13" s="1">
         <v>33696</v>
       </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -6708,6 +12303,10 @@
       <c r="G14" s="1">
         <v>57420</v>
       </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -6730,6 +12329,10 @@
       </c>
       <c r="G15" s="1">
         <v>17880</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>2024</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="5"/>
@@ -6756,8 +12359,12 @@
       <c r="G16" s="1">
         <v>12987</v>
       </c>
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>45307</v>
       </c>
@@ -6779,8 +12386,12 @@
       <c r="G17" s="1">
         <v>48627</v>
       </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>45308</v>
       </c>
@@ -6802,8 +12413,12 @@
       <c r="G18" s="1">
         <v>52992</v>
       </c>
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>45309</v>
       </c>
@@ -6825,8 +12440,12 @@
       <c r="G19" s="1">
         <v>17325</v>
       </c>
+      <c r="H19">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>45310</v>
       </c>
@@ -6848,8 +12467,12 @@
       <c r="G20" s="1">
         <v>10008</v>
       </c>
+      <c r="H20">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>45311</v>
       </c>
@@ -6871,8 +12494,12 @@
       <c r="G21" s="1">
         <v>74014</v>
       </c>
+      <c r="H21">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>45312</v>
       </c>
@@ -6894,8 +12521,12 @@
       <c r="G22" s="1">
         <v>47120</v>
       </c>
+      <c r="H22">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>45313</v>
       </c>
@@ -6917,8 +12548,12 @@
       <c r="G23" s="1">
         <v>37500</v>
       </c>
+      <c r="H23">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>45314</v>
       </c>
@@ -6940,8 +12575,12 @@
       <c r="G24" s="1">
         <v>6083</v>
       </c>
+      <c r="H24">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>45315</v>
       </c>
@@ -6963,8 +12602,12 @@
       <c r="G25" s="1">
         <v>47566</v>
       </c>
+      <c r="H25">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>45316</v>
       </c>
@@ -6986,8 +12629,12 @@
       <c r="G26" s="1">
         <v>29848</v>
       </c>
+      <c r="H26">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>45317</v>
       </c>
@@ -7009,8 +12656,12 @@
       <c r="G27" s="1">
         <v>14175</v>
       </c>
+      <c r="H27">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>45318</v>
       </c>
@@ -7032,8 +12683,12 @@
       <c r="G28" s="1">
         <v>72980</v>
       </c>
+      <c r="H28">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>45319</v>
       </c>
@@ -7055,8 +12710,12 @@
       <c r="G29" s="1">
         <v>36081</v>
       </c>
+      <c r="H29">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>45320</v>
       </c>
@@ -7078,8 +12737,12 @@
       <c r="G30" s="1">
         <v>15387</v>
       </c>
+      <c r="H30">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>45321</v>
       </c>
@@ -7101,8 +12764,12 @@
       <c r="G31" s="1">
         <v>42372</v>
       </c>
+      <c r="H31">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>45322</v>
       </c>
@@ -7124,8 +12791,12 @@
       <c r="G32" s="1">
         <v>47850</v>
       </c>
+      <c r="H32">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>45323</v>
       </c>
@@ -7147,8 +12818,12 @@
       <c r="G33" s="1">
         <v>15283</v>
       </c>
+      <c r="H33">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>45324</v>
       </c>
@@ -7170,8 +12845,12 @@
       <c r="G34" s="1">
         <v>55800</v>
       </c>
+      <c r="H34">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>45325</v>
       </c>
@@ -7193,8 +12872,12 @@
       <c r="G35" s="1">
         <v>21630</v>
       </c>
+      <c r="H35">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>45326</v>
       </c>
@@ -7216,8 +12899,12 @@
       <c r="G36" s="1">
         <v>95000</v>
       </c>
+      <c r="H36">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>45327</v>
       </c>
@@ -7239,8 +12926,12 @@
       <c r="G37" s="1">
         <v>49600</v>
       </c>
+      <c r="H37">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>45328</v>
       </c>
@@ -7262,8 +12953,12 @@
       <c r="G38" s="1">
         <v>44880</v>
       </c>
+      <c r="H38">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>45329</v>
       </c>
@@ -7285,8 +12980,12 @@
       <c r="G39" s="1">
         <v>46018</v>
       </c>
+      <c r="H39">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>45330</v>
       </c>
@@ -7308,8 +13007,12 @@
       <c r="G40" s="1">
         <v>20832</v>
       </c>
+      <c r="H40">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>45331</v>
       </c>
@@ -7331,8 +13034,12 @@
       <c r="G41" s="1">
         <v>38500</v>
       </c>
+      <c r="H41">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>45332</v>
       </c>
@@ -7354,8 +13061,12 @@
       <c r="G42" s="1">
         <v>3570</v>
       </c>
+      <c r="H42">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>45333</v>
       </c>
@@ -7377,10 +13088,14 @@
       <c r="G43" s="1">
         <v>37240</v>
       </c>
+      <c r="H43">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>45334</v>
+        <v>45700</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
@@ -7400,10 +13115,14 @@
       <c r="G44" s="1">
         <v>72000</v>
       </c>
+      <c r="H44">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>45335</v>
+        <v>45701</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>12</v>
@@ -7423,10 +13142,14 @@
       <c r="G45" s="1">
         <v>24570</v>
       </c>
+      <c r="H45">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>45336</v>
+        <v>45702</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>8</v>
@@ -7446,10 +13169,14 @@
       <c r="G46" s="1">
         <v>38148</v>
       </c>
+      <c r="H46">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>45337</v>
+        <v>45703</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>10</v>
@@ -7469,10 +13196,14 @@
       <c r="G47" s="1">
         <v>27200</v>
       </c>
+      <c r="H47">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>45338</v>
+        <v>45704</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
@@ -7492,10 +13223,14 @@
       <c r="G48" s="1">
         <v>32655</v>
       </c>
+      <c r="H48">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>45339</v>
+        <v>45705</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>12</v>
@@ -7515,10 +13250,14 @@
       <c r="G49" s="1">
         <v>7826</v>
       </c>
+      <c r="H49">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>45340</v>
+        <v>45706</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>8</v>
@@ -7538,10 +13277,14 @@
       <c r="G50" s="1">
         <v>81340</v>
       </c>
+      <c r="H50">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>45341</v>
+        <v>45707</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>10</v>
@@ -7561,10 +13304,14 @@
       <c r="G51" s="1">
         <v>32970</v>
       </c>
+      <c r="H51">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>45342</v>
+        <v>45708</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
@@ -7584,10 +13331,14 @@
       <c r="G52" s="1">
         <v>18018</v>
       </c>
+      <c r="H52">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>45343</v>
+        <v>45709</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>12</v>
@@ -7607,10 +13358,14 @@
       <c r="G53" s="1">
         <v>58349</v>
       </c>
+      <c r="H53">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>45344</v>
+        <v>45710</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>8</v>
@@ -7630,10 +13385,14 @@
       <c r="G54" s="1">
         <v>52780</v>
       </c>
+      <c r="H54">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>45345</v>
+        <v>46076</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>10</v>
@@ -7653,10 +13412,14 @@
       <c r="G55" s="1">
         <v>5880</v>
       </c>
+      <c r="H55">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>45346</v>
+        <v>46077</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>12</v>
@@ -7676,10 +13439,14 @@
       <c r="G56" s="1">
         <v>42504</v>
       </c>
+      <c r="H56">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>45347</v>
+        <v>46078</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>7</v>
@@ -7699,10 +13466,14 @@
       <c r="G57" s="1">
         <v>70434</v>
       </c>
+      <c r="H57">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>45348</v>
+        <v>46079</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>8</v>
@@ -7722,10 +13493,14 @@
       <c r="G58" s="1">
         <v>38000</v>
       </c>
+      <c r="H58">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>45349</v>
+        <v>46080</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>10</v>
@@ -7745,10 +13520,14 @@
       <c r="G59" s="1">
         <v>23280</v>
       </c>
+      <c r="H59">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>45350</v>
+        <v>46081</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>12</v>
@@ -7767,6 +13546,10 @@
       </c>
       <c r="G60" s="1">
         <v>417</v>
+      </c>
+      <c r="H60">
+        <f t="shared" si="0"/>
+        <v>2026</v>
       </c>
     </row>
   </sheetData>
@@ -7780,13 +13563,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAD0F22C-D487-40E1-AD1C-42A81DF02B99}">
-  <dimension ref="A3:B8"/>
+  <dimension ref="A3:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7802,7 +13585,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="8">
-        <v>600931</v>
+        <v>69450</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7810,7 +13593,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="8">
-        <v>602288</v>
+        <v>33301</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7818,7 +13601,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="8">
-        <v>575379</v>
+        <v>126790</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7826,7 +13609,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="8">
-        <v>410724</v>
+        <v>37455</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7834,15 +13617,87 @@
         <v>23</v>
       </c>
       <c r="B8" s="8">
-        <v>2189322</v>
+        <v>266996</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="8">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="8">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="8">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="8">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="8">
+        <v>242</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId4"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A274FA-0A39-446B-8148-EAF88ACEE9B3}">
   <dimension ref="A3:B10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
